--- a/output/yearly_total_coral_cover_iteration_81_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_81_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.302284829964475</v>
+        <v>1.287283725043584</v>
       </c>
       <c r="C3" t="n">
-        <v>4.667284436668639</v>
+        <v>4.631421193032504</v>
       </c>
       <c r="D3" t="n">
-        <v>6.14190699773459</v>
+        <v>6.056887646546816</v>
       </c>
       <c r="E3" t="n">
-        <v>12.1114762643677</v>
+        <v>11.9755925646229</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.501139566316369</v>
+        <v>1.462089271197424</v>
       </c>
       <c r="C4" t="n">
-        <v>5.279560820437048</v>
+        <v>5.113983234231739</v>
       </c>
       <c r="D4" t="n">
-        <v>6.510158239257394</v>
+        <v>6.287019540442675</v>
       </c>
       <c r="E4" t="n">
-        <v>13.29085862601081</v>
+        <v>12.86309204587184</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.751322316658055</v>
+        <v>1.696098396901963</v>
       </c>
       <c r="C5" t="n">
-        <v>6.08314025672003</v>
+        <v>5.743917178511898</v>
       </c>
       <c r="D5" t="n">
-        <v>6.859185420401069</v>
+        <v>6.534328076607558</v>
       </c>
       <c r="E5" t="n">
-        <v>14.69364799377915</v>
+        <v>13.97434365202142</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>2.025699511909003</v>
+        <v>1.959412257892873</v>
       </c>
       <c r="C6" t="n">
-        <v>7.081251457651357</v>
+        <v>6.484887057104682</v>
       </c>
       <c r="D6" t="n">
-        <v>7.225172371622977</v>
+        <v>6.899573915750214</v>
       </c>
       <c r="E6" t="n">
-        <v>16.33212334118334</v>
+        <v>15.34387323074777</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.315992267781833</v>
+        <v>2.246915830330543</v>
       </c>
       <c r="C7" t="n">
-        <v>8.216547493432673</v>
+        <v>7.346828298362938</v>
       </c>
       <c r="D7" t="n">
-        <v>7.603135393421845</v>
+        <v>7.310476164416087</v>
       </c>
       <c r="E7" t="n">
-        <v>18.13567515463635</v>
+        <v>16.90422029310957</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.458616512291295</v>
+        <v>1.419600205624929</v>
       </c>
       <c r="C8" t="n">
-        <v>5.871592351496502</v>
+        <v>4.959235594409908</v>
       </c>
       <c r="D8" t="n">
-        <v>5.86233864703414</v>
+        <v>5.567746162888318</v>
       </c>
       <c r="E8" t="n">
-        <v>13.19254751082194</v>
+        <v>11.94658196292316</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.826074206400119</v>
+        <v>1.793301275237888</v>
       </c>
       <c r="C9" t="n">
-        <v>7.30839508824164</v>
+        <v>6.008587945154794</v>
       </c>
       <c r="D9" t="n">
-        <v>6.417118210153161</v>
+        <v>6.18275395969357</v>
       </c>
       <c r="E9" t="n">
-        <v>15.55158750479492</v>
+        <v>13.98464318008625</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.208211645708031</v>
+        <v>2.185572471441976</v>
       </c>
       <c r="C10" t="n">
-        <v>8.864390996210462</v>
+        <v>7.199340667122555</v>
       </c>
       <c r="D10" t="n">
-        <v>6.947432292477687</v>
+        <v>6.747911132709583</v>
       </c>
       <c r="E10" t="n">
-        <v>18.02003493439618</v>
+        <v>16.13282427127411</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.59305510426693</v>
+        <v>2.577281046738831</v>
       </c>
       <c r="C11" t="n">
-        <v>10.51809234211759</v>
+        <v>8.497162717584031</v>
       </c>
       <c r="D11" t="n">
-        <v>7.442780770998707</v>
+        <v>7.261106926546852</v>
       </c>
       <c r="E11" t="n">
-        <v>20.55392821738323</v>
+        <v>18.33555069086971</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.964903965643712</v>
+        <v>3.001734430443546</v>
       </c>
       <c r="C12" t="n">
-        <v>12.17882703256072</v>
+        <v>9.911728886735304</v>
       </c>
       <c r="D12" t="n">
-        <v>7.91113130594746</v>
+        <v>7.775456032981983</v>
       </c>
       <c r="E12" t="n">
-        <v>23.05486230415189</v>
+        <v>20.68891935016083</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.320434805447762</v>
+        <v>3.417404233515084</v>
       </c>
       <c r="C13" t="n">
-        <v>13.83758930949096</v>
+        <v>11.41160842635908</v>
       </c>
       <c r="D13" t="n">
-        <v>8.414239425183952</v>
+        <v>8.328589528362292</v>
       </c>
       <c r="E13" t="n">
-        <v>25.57226354012267</v>
+        <v>23.15760218823646</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.906603129032518</v>
+        <v>1.984180832622101</v>
       </c>
       <c r="C14" t="n">
-        <v>9.610995865310915</v>
+        <v>8.110325777030368</v>
       </c>
       <c r="D14" t="n">
-        <v>6.35806320458249</v>
+        <v>6.357631235592622</v>
       </c>
       <c r="E14" t="n">
-        <v>17.87566219892592</v>
+        <v>16.45213784524509</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.95545489479584</v>
+        <v>2.05076296192412</v>
       </c>
       <c r="C15" t="n">
-        <v>10.30062454015909</v>
+        <v>8.769304288551954</v>
       </c>
       <c r="D15" t="n">
-        <v>6.363443182001763</v>
+        <v>6.410449262081101</v>
       </c>
       <c r="E15" t="n">
-        <v>18.61952261695669</v>
+        <v>17.23051651255717</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.266816179197716</v>
+        <v>2.404791001552562</v>
       </c>
       <c r="C16" t="n">
-        <v>12.06312674116226</v>
+        <v>10.37796662429965</v>
       </c>
       <c r="D16" t="n">
-        <v>6.771457527886739</v>
+        <v>6.89242848000403</v>
       </c>
       <c r="E16" t="n">
-        <v>21.10140044824671</v>
+        <v>19.67518610585624</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.816301975195897</v>
+        <v>1.944960011837441</v>
       </c>
       <c r="C17" t="n">
-        <v>10.97353405160394</v>
+        <v>9.591841967601059</v>
       </c>
       <c r="D17" t="n">
-        <v>6.2554705694887</v>
+        <v>6.409546054193194</v>
       </c>
       <c r="E17" t="n">
-        <v>19.04530659628853</v>
+        <v>17.94634803363169</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2.069916859633975</v>
+        <v>2.23680415187889</v>
       </c>
       <c r="C18" t="n">
-        <v>12.77546324040966</v>
+        <v>11.21496544703231</v>
       </c>
       <c r="D18" t="n">
-        <v>6.691886876457533</v>
+        <v>6.851116536609325</v>
       </c>
       <c r="E18" t="n">
-        <v>21.53726697650117</v>
+        <v>20.30288613552053</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2.076258949803409</v>
+        <v>2.257744830410475</v>
       </c>
       <c r="C19" t="n">
-        <v>13.62045348945489</v>
+        <v>12.01430442783006</v>
       </c>
       <c r="D19" t="n">
-        <v>6.771997489124074</v>
+        <v>6.959982539533253</v>
       </c>
       <c r="E19" t="n">
-        <v>22.46870992838237</v>
+        <v>21.23203179777379</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.306999112732537</v>
+        <v>2.539182444786908</v>
       </c>
       <c r="C20" t="n">
-        <v>15.67835375718888</v>
+        <v>13.82985045729369</v>
       </c>
       <c r="D20" t="n">
-        <v>7.169448229711351</v>
+        <v>7.38988985922293</v>
       </c>
       <c r="E20" t="n">
-        <v>25.15480109963277</v>
+        <v>23.75892276130353</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.367329115089745</v>
+        <v>1.526627497580833</v>
       </c>
       <c r="C21" t="n">
-        <v>11.57321500178901</v>
+        <v>10.19587206011595</v>
       </c>
       <c r="D21" t="n">
-        <v>5.972089094657857</v>
+        <v>6.176822760901488</v>
       </c>
       <c r="E21" t="n">
-        <v>18.91263321153662</v>
+        <v>17.89932231859827</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_81_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_81_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.287283725043584</v>
+        <v>1.2583908901076</v>
       </c>
       <c r="C3" t="n">
-        <v>4.631421193032504</v>
+        <v>4.633482863211423</v>
       </c>
       <c r="D3" t="n">
-        <v>6.056887646546816</v>
+        <v>6.050280484497234</v>
       </c>
       <c r="E3" t="n">
-        <v>11.9755925646229</v>
+        <v>11.94215423781626</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.462089271197424</v>
+        <v>1.391890238334107</v>
       </c>
       <c r="C4" t="n">
-        <v>5.113983234231739</v>
+        <v>5.168863557679544</v>
       </c>
       <c r="D4" t="n">
-        <v>6.287019540442675</v>
+        <v>6.277212556814587</v>
       </c>
       <c r="E4" t="n">
-        <v>12.86309204587184</v>
+        <v>12.83796635282824</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.696098396901963</v>
+        <v>1.568512016875032</v>
       </c>
       <c r="C5" t="n">
-        <v>5.743917178511898</v>
+        <v>5.845346056552583</v>
       </c>
       <c r="D5" t="n">
-        <v>6.534328076607558</v>
+        <v>6.499998752883526</v>
       </c>
       <c r="E5" t="n">
-        <v>13.97434365202142</v>
+        <v>13.91385682631114</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.959412257892873</v>
+        <v>1.776684111753465</v>
       </c>
       <c r="C6" t="n">
-        <v>6.484887057104682</v>
+        <v>6.690907103622667</v>
       </c>
       <c r="D6" t="n">
-        <v>6.899573915750214</v>
+        <v>6.784147277386715</v>
       </c>
       <c r="E6" t="n">
-        <v>15.34387323074777</v>
+        <v>15.25173849276285</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.246915830330543</v>
+        <v>2.000855925714111</v>
       </c>
       <c r="C7" t="n">
-        <v>7.346828298362938</v>
+        <v>7.674787438519481</v>
       </c>
       <c r="D7" t="n">
-        <v>7.310476164416087</v>
+        <v>7.066312869657405</v>
       </c>
       <c r="E7" t="n">
-        <v>16.90422029310957</v>
+        <v>16.741956233891</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.419600205624929</v>
+        <v>1.216250878794184</v>
       </c>
       <c r="C8" t="n">
-        <v>4.959235594409908</v>
+        <v>5.334176791853723</v>
       </c>
       <c r="D8" t="n">
-        <v>5.567746162888318</v>
+        <v>5.230292535239245</v>
       </c>
       <c r="E8" t="n">
-        <v>11.94658196292316</v>
+        <v>11.78072020588715</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.793301275237888</v>
+        <v>1.514815102094505</v>
       </c>
       <c r="C9" t="n">
-        <v>6.008587945154794</v>
+        <v>6.584030036419462</v>
       </c>
       <c r="D9" t="n">
-        <v>6.18275395969357</v>
+        <v>5.593705851762234</v>
       </c>
       <c r="E9" t="n">
-        <v>13.98464318008625</v>
+        <v>13.6925509902762</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.185572471441976</v>
+        <v>1.830104397677533</v>
       </c>
       <c r="C10" t="n">
-        <v>7.199340667122555</v>
+        <v>8.014288997912519</v>
       </c>
       <c r="D10" t="n">
-        <v>6.747911132709583</v>
+        <v>5.948869811212346</v>
       </c>
       <c r="E10" t="n">
-        <v>16.13282427127411</v>
+        <v>15.7932632068024</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.577281046738831</v>
+        <v>2.141643435539501</v>
       </c>
       <c r="C11" t="n">
-        <v>8.497162717584031</v>
+        <v>9.560139965619031</v>
       </c>
       <c r="D11" t="n">
-        <v>7.261106926546852</v>
+        <v>6.287022813230972</v>
       </c>
       <c r="E11" t="n">
-        <v>18.33555069086971</v>
+        <v>17.98880621438951</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.001734430443546</v>
+        <v>2.472310051898462</v>
       </c>
       <c r="C12" t="n">
-        <v>9.911728886735304</v>
+        <v>11.18697529150486</v>
       </c>
       <c r="D12" t="n">
-        <v>7.775456032981983</v>
+        <v>6.619954639334907</v>
       </c>
       <c r="E12" t="n">
-        <v>20.68891935016083</v>
+        <v>20.27923998273823</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.417404233515084</v>
+        <v>2.816138923192264</v>
       </c>
       <c r="C13" t="n">
-        <v>11.41160842635908</v>
+        <v>12.85447384334333</v>
       </c>
       <c r="D13" t="n">
-        <v>8.328589528362292</v>
+        <v>6.944844122002315</v>
       </c>
       <c r="E13" t="n">
-        <v>23.15760218823646</v>
+        <v>22.61545688853791</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.984180832622101</v>
+        <v>1.642473726681956</v>
       </c>
       <c r="C14" t="n">
-        <v>8.110325777030368</v>
+        <v>9.006710518392918</v>
       </c>
       <c r="D14" t="n">
-        <v>6.357631235592622</v>
+        <v>5.282646951873492</v>
       </c>
       <c r="E14" t="n">
-        <v>16.45213784524509</v>
+        <v>15.93183119694837</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2.05076296192412</v>
+        <v>1.69885549733685</v>
       </c>
       <c r="C15" t="n">
-        <v>8.769304288551954</v>
+        <v>9.70247511639263</v>
       </c>
       <c r="D15" t="n">
-        <v>6.410449262081101</v>
+        <v>5.181183326639585</v>
       </c>
       <c r="E15" t="n">
-        <v>17.23051651255717</v>
+        <v>16.58251394036906</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.404791001552562</v>
+        <v>2.00394341390859</v>
       </c>
       <c r="C16" t="n">
-        <v>10.37796662429965</v>
+        <v>11.44561725266806</v>
       </c>
       <c r="D16" t="n">
-        <v>6.89242848000403</v>
+        <v>5.528280227476045</v>
       </c>
       <c r="E16" t="n">
-        <v>19.67518610585624</v>
+        <v>18.97784089405269</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.944960011837441</v>
+        <v>1.630496404690145</v>
       </c>
       <c r="C17" t="n">
-        <v>9.591841967601059</v>
+        <v>10.50878450589054</v>
       </c>
       <c r="D17" t="n">
-        <v>6.409546054193194</v>
+        <v>5.053094703666503</v>
       </c>
       <c r="E17" t="n">
-        <v>17.94634803363169</v>
+        <v>17.19237561424719</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2.23680415187889</v>
+        <v>1.890306117142021</v>
       </c>
       <c r="C18" t="n">
-        <v>11.21496544703231</v>
+        <v>12.33759394683854</v>
       </c>
       <c r="D18" t="n">
-        <v>6.851116536609325</v>
+        <v>5.359498162161932</v>
       </c>
       <c r="E18" t="n">
-        <v>20.30288613552053</v>
+        <v>19.58739822614249</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2.257744830410475</v>
+        <v>1.921260622256923</v>
       </c>
       <c r="C19" t="n">
-        <v>12.01430442783006</v>
+        <v>13.27419107416704</v>
       </c>
       <c r="D19" t="n">
-        <v>6.959982539533253</v>
+        <v>5.377640859736414</v>
       </c>
       <c r="E19" t="n">
-        <v>21.23203179777379</v>
+        <v>20.57309255616038</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.539182444786908</v>
+        <v>2.159668234756218</v>
       </c>
       <c r="C20" t="n">
-        <v>13.82985045729369</v>
+        <v>15.30367956334013</v>
       </c>
       <c r="D20" t="n">
-        <v>7.38988985922293</v>
+        <v>5.667698218956134</v>
       </c>
       <c r="E20" t="n">
-        <v>23.75892276130353</v>
+        <v>23.13104601705248</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.526627497580833</v>
+        <v>1.296996709557504</v>
       </c>
       <c r="C21" t="n">
-        <v>10.19587206011595</v>
+        <v>11.29347581094093</v>
       </c>
       <c r="D21" t="n">
-        <v>6.176822760901488</v>
+        <v>4.665088375994078</v>
       </c>
       <c r="E21" t="n">
-        <v>17.89932231859827</v>
+        <v>17.25556089649251</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_81_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_81_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.2583908901076</v>
+        <v>2.630376510917924</v>
       </c>
       <c r="C3" t="n">
-        <v>4.633482863211423</v>
+        <v>7.892659662878314</v>
       </c>
       <c r="D3" t="n">
-        <v>6.050280484497234</v>
+        <v>8.158998633264346</v>
       </c>
       <c r="E3" t="n">
-        <v>11.94215423781626</v>
+        <v>18.68203480706059</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.391890238334107</v>
+        <v>1.15276788096031</v>
       </c>
       <c r="C4" t="n">
-        <v>5.168863557679544</v>
+        <v>4.922910936809187</v>
       </c>
       <c r="D4" t="n">
-        <v>6.277212556814587</v>
+        <v>5.724000122573329</v>
       </c>
       <c r="E4" t="n">
-        <v>12.83796635282824</v>
+        <v>11.79967894034283</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.568512016875032</v>
+        <v>1.306879754487647</v>
       </c>
       <c r="C5" t="n">
-        <v>5.845346056552583</v>
+        <v>6.024197051616916</v>
       </c>
       <c r="D5" t="n">
-        <v>6.499998752883526</v>
+        <v>6.04793970617331</v>
       </c>
       <c r="E5" t="n">
-        <v>13.91385682631114</v>
+        <v>13.37901651227787</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.776684111753465</v>
+        <v>1.480100666566663</v>
       </c>
       <c r="C6" t="n">
-        <v>6.690907103622667</v>
+        <v>7.38069442098704</v>
       </c>
       <c r="D6" t="n">
-        <v>6.784147277386715</v>
+        <v>6.340988674541146</v>
       </c>
       <c r="E6" t="n">
-        <v>15.25173849276285</v>
+        <v>15.20178376209485</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.000855925714111</v>
+        <v>1.649139641603017</v>
       </c>
       <c r="C7" t="n">
-        <v>7.674787438519481</v>
+        <v>8.926948249283141</v>
       </c>
       <c r="D7" t="n">
-        <v>7.066312869657405</v>
+        <v>6.695718244052629</v>
       </c>
       <c r="E7" t="n">
-        <v>16.741956233891</v>
+        <v>17.27180613493879</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.216250878794184</v>
+        <v>1.810247927723894</v>
       </c>
       <c r="C8" t="n">
-        <v>5.334176791853723</v>
+        <v>10.57636483318839</v>
       </c>
       <c r="D8" t="n">
-        <v>5.230292535239245</v>
+        <v>6.993949389696731</v>
       </c>
       <c r="E8" t="n">
-        <v>11.78072020588715</v>
+        <v>19.38056215060902</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.514815102094505</v>
+        <v>1.938028344647371</v>
       </c>
       <c r="C9" t="n">
-        <v>6.584030036419462</v>
+        <v>12.40102484137432</v>
       </c>
       <c r="D9" t="n">
-        <v>5.593705851762234</v>
+        <v>7.305088297506074</v>
       </c>
       <c r="E9" t="n">
-        <v>13.6925509902762</v>
+        <v>21.64414148352776</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.830104397677533</v>
+        <v>1.169595309977395</v>
       </c>
       <c r="C10" t="n">
-        <v>8.014288997912519</v>
+        <v>8.763413802326474</v>
       </c>
       <c r="D10" t="n">
-        <v>5.948869811212346</v>
+        <v>5.722931344797059</v>
       </c>
       <c r="E10" t="n">
-        <v>15.7932632068024</v>
+        <v>15.65594045710093</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.141643435539501</v>
+        <v>1.092852091936422</v>
       </c>
       <c r="C11" t="n">
-        <v>9.560139965619031</v>
+        <v>9.664137868541795</v>
       </c>
       <c r="D11" t="n">
-        <v>6.287022813230972</v>
+        <v>5.510520411506219</v>
       </c>
       <c r="E11" t="n">
-        <v>17.98880621438951</v>
+        <v>16.26751037198444</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.472310051898462</v>
+        <v>1.165894121132385</v>
       </c>
       <c r="C12" t="n">
-        <v>11.18697529150486</v>
+        <v>11.65703662077761</v>
       </c>
       <c r="D12" t="n">
-        <v>6.619954639334907</v>
+        <v>5.797583440227987</v>
       </c>
       <c r="E12" t="n">
-        <v>20.27923998273823</v>
+        <v>18.62051418213798</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.816138923192264</v>
+        <v>0.9087842148671874</v>
       </c>
       <c r="C13" t="n">
-        <v>12.85447384334333</v>
+        <v>11.20411713490038</v>
       </c>
       <c r="D13" t="n">
-        <v>6.944844122002315</v>
+        <v>5.210135066437823</v>
       </c>
       <c r="E13" t="n">
-        <v>22.61545688853791</v>
+        <v>17.32303641620539</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.642473726681956</v>
+        <v>0.9761321073785187</v>
       </c>
       <c r="C14" t="n">
-        <v>9.006710518392918</v>
+        <v>13.24043858809503</v>
       </c>
       <c r="D14" t="n">
-        <v>5.282646951873492</v>
+        <v>5.467892926187822</v>
       </c>
       <c r="E14" t="n">
-        <v>15.93183119694837</v>
+        <v>19.68446362166137</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.69885549733685</v>
+        <v>0.9340936706826704</v>
       </c>
       <c r="C15" t="n">
-        <v>9.70247511639263</v>
+        <v>14.34897900834532</v>
       </c>
       <c r="D15" t="n">
-        <v>5.181183326639585</v>
+        <v>5.425864306969016</v>
       </c>
       <c r="E15" t="n">
-        <v>16.58251394036906</v>
+        <v>20.70893698599701</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.00394341390859</v>
+        <v>1.005702348230433</v>
       </c>
       <c r="C16" t="n">
-        <v>11.44561725266806</v>
+        <v>16.62521014802676</v>
       </c>
       <c r="D16" t="n">
-        <v>5.528280227476045</v>
+        <v>5.750086486296526</v>
       </c>
       <c r="E16" t="n">
-        <v>18.97784089405269</v>
+        <v>23.38099898255372</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.630496404690145</v>
+        <v>0.5962055633120456</v>
       </c>
       <c r="C17" t="n">
-        <v>10.50878450589054</v>
+        <v>12.23812326944426</v>
       </c>
       <c r="D17" t="n">
-        <v>5.053094703666503</v>
+        <v>4.728391467963913</v>
       </c>
       <c r="E17" t="n">
-        <v>17.19237561424719</v>
+        <v>17.56272030072022</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.890306117142021</v>
+        <v>0.4704633173521141</v>
       </c>
       <c r="C18" t="n">
-        <v>12.33759394683854</v>
+        <v>11.03227201674902</v>
       </c>
       <c r="D18" t="n">
-        <v>5.359498162161932</v>
+        <v>4.24381061862473</v>
       </c>
       <c r="E18" t="n">
-        <v>19.58739822614249</v>
+        <v>15.74654595272587</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.921260622256923</v>
+        <v>0.5444772767752811</v>
       </c>
       <c r="C19" t="n">
-        <v>13.27419107416704</v>
+        <v>13.50414583893277</v>
       </c>
       <c r="D19" t="n">
-        <v>5.377640859736414</v>
+        <v>4.660258177289185</v>
       </c>
       <c r="E19" t="n">
-        <v>20.57309255616038</v>
+        <v>18.70888129299724</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.159668234756218</v>
+        <v>0.6119822489192918</v>
       </c>
       <c r="C20" t="n">
-        <v>15.30367956334013</v>
+        <v>16.07228984099496</v>
       </c>
       <c r="D20" t="n">
-        <v>5.667698218956134</v>
+        <v>5.025978832075206</v>
       </c>
       <c r="E20" t="n">
-        <v>23.13104601705248</v>
+        <v>21.71025092198946</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.296996709557504</v>
+        <v>0.6670681126045803</v>
       </c>
       <c r="C21" t="n">
-        <v>11.29347581094093</v>
+        <v>18.58276598290969</v>
       </c>
       <c r="D21" t="n">
-        <v>4.665088375994078</v>
+        <v>5.348767659754515</v>
       </c>
       <c r="E21" t="n">
-        <v>17.25556089649251</v>
+        <v>24.59860175526878</v>
       </c>
     </row>
   </sheetData>
